--- a/PANDA_POWER/notebooks/results_consolidados.xlsx
+++ b/PANDA_POWER/notebooks/results_consolidados.xlsx
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>[-46.45290714183709, -49.25700405149819, -45.36934641352421, -37.69687424648752, -56.73327079522718]</t>
+          <t>[-49.16009044238672, -43.464639750810285, -41.111615991833396, -44.62430892569929, -44.27357863881914]</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-47.10188052971483</v>
+        <v>-44.52684674990977</v>
       </c>
       <c r="D2" t="n">
-        <v>-47.10188052971483</v>
+        <v>-44.52684674990977</v>
       </c>
       <c r="E2" t="n">
-        <v>-56.73327079522718</v>
+        <v>-49.16009044238672</v>
       </c>
       <c r="F2" t="n">
-        <v>-37.69687424648752</v>
+        <v>-41.1116159918334</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>[-49.38708693010342, -40.960669090051205, -45.538975158931294, -54.61600473267666, -44.656631380441226]</t>
+          <t>[-38.14244616653527, -44.962982208378925, -50.29560615626679, -41.02436817776806, -50.21512373440133]</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-47.03187345844076</v>
+        <v>-44.92810528867007</v>
       </c>
       <c r="D3" t="n">
-        <v>-47.03187345844076</v>
+        <v>-44.92810528867007</v>
       </c>
       <c r="E3" t="n">
-        <v>-54.61600473267666</v>
+        <v>-50.29560615626679</v>
       </c>
       <c r="F3" t="n">
-        <v>-40.9606690900512</v>
+        <v>-38.14244616653527</v>
       </c>
     </row>
     <row r="4">
@@ -510,20 +510,20 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[-51.92168469677282, -35.48267510581329, -40.45558897259285, -53.02976132914512, -50.4935695902672]</t>
+          <t>[-47.47740411375018, -44.44220053370135, -43.03780891109198, -50.16112259427547, -46.66368019006346]</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-46.27665593891826</v>
+        <v>-46.35644326857649</v>
       </c>
       <c r="D4" t="n">
-        <v>-46.27665593891826</v>
+        <v>-46.35644326857649</v>
       </c>
       <c r="E4" t="n">
-        <v>-53.02976132914512</v>
+        <v>-50.16112259427547</v>
       </c>
       <c r="F4" t="n">
-        <v>-35.48267510581329</v>
+        <v>-43.03780891109198</v>
       </c>
     </row>
     <row r="5">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[-54.1072789521467, -49.92152424997123, -40.71604484483518, -38.751559814854645, -39.854731107076915]</t>
+          <t>[-57.11398467942161, -37.69697917387816, -48.740753735126255, -47.18454383020805, -33.3154093632523]</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-44.67022779377694</v>
+        <v>-44.81033415637727</v>
       </c>
       <c r="D5" t="n">
-        <v>-44.67022779377694</v>
+        <v>-44.81033415637727</v>
       </c>
       <c r="E5" t="n">
-        <v>-54.1072789521467</v>
+        <v>-57.11398467942161</v>
       </c>
       <c r="F5" t="n">
-        <v>-38.75155981485464</v>
+        <v>-33.3154093632523</v>
       </c>
     </row>
     <row r="6">
@@ -554,20 +554,20 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>[-61.59467058576785, -45.98016194124253, -48.03105488342257, -38.28478532949901, -46.41123800886115]</t>
+          <t>[-53.95040357869742, -48.10311959038408, -46.3205118564382, -44.03581531851657, -35.91811494600038]</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-48.06038214975862</v>
+        <v>-45.66559305800733</v>
       </c>
       <c r="D6" t="n">
-        <v>-48.06038214975862</v>
+        <v>-45.66559305800733</v>
       </c>
       <c r="E6" t="n">
-        <v>-61.59467058576785</v>
+        <v>-53.95040357869742</v>
       </c>
       <c r="F6" t="n">
-        <v>-38.28478532949901</v>
+        <v>-35.91811494600038</v>
       </c>
     </row>
   </sheetData>

--- a/PANDA_POWER/notebooks/results_consolidados.xlsx
+++ b/PANDA_POWER/notebooks/results_consolidados.xlsx
@@ -1,37 +1,78 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+  <si>
+    <t>execution</t>
+  </si>
+  <si>
+    <t>solution_variables</t>
+  </si>
+  <si>
+    <t>best_fitness</t>
+  </si>
+  <si>
+    <t>mean_solution</t>
+  </si>
+  <si>
+    <t>min_solution</t>
+  </si>
+  <si>
+    <t>max_solution</t>
+  </si>
+  <si>
+    <t>[-0.009947378528738698, 0.004459406837340901, 0.0019962887981140893, 0.0017006735542902576, 0.0033131360891133187]</t>
+  </si>
+  <si>
+    <t>[-0.006056678831586502, 0.0004560268699975623, 0.0015088817367165065, 0.0002216422400582352, -0.0033350553372637213]</t>
+  </si>
+  <si>
+    <t>[-0.007437649408662244, -0.00023859357258367627, -0.004384958754194064, 0.0022839728102715786, -0.0037274771918312556]</t>
+  </si>
+  <si>
+    <t>[0.0016269709884116478, -0.003149451149432465, -0.00011283725843748427, 0.0026473583372079177, -0.0015736696023918272]</t>
+  </si>
+  <si>
+    <t>[0.00041424964700103196, -0.0038276063129415684, 5.470105700222487e-05, 0.0009734866626195625, -0.00430801040561702]</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +87,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -420,157 +403,131 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>execution</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>solution_variables</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>best_fitness</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>mean_solution</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>min_solution</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>max_solution</t>
-        </is>
+    <row r="1" spans="1:6">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
+    <row r="2" spans="1:6">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>[-49.16009044238672, -43.464639750810285, -41.111615991833396, -44.62430892569929, -44.27357863881914]</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>-44.52684674990977</v>
-      </c>
-      <c r="D2" t="n">
-        <v>-44.52684674990977</v>
-      </c>
-      <c r="E2" t="n">
-        <v>-49.16009044238672</v>
-      </c>
-      <c r="F2" t="n">
-        <v>-41.1116159918334</v>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>0.02711170047837008</v>
+      </c>
+      <c r="D2">
+        <v>0.0003044253500239736</v>
+      </c>
+      <c r="E2">
+        <v>-0.009947378528738698</v>
+      </c>
+      <c r="F2">
+        <v>0.004459406837340901</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
+    <row r="3" spans="1:6">
+      <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>[-38.14244616653527, -44.962982208378925, -50.29560615626679, -41.02436817776806, -50.21512373440133]</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>-44.92810528867007</v>
-      </c>
-      <c r="D3" t="n">
-        <v>-44.92810528867007</v>
-      </c>
-      <c r="E3" t="n">
-        <v>-50.29560615626679</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-38.14244616653527</v>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>0.009986053024675812</v>
+      </c>
+      <c r="D3">
+        <v>-0.001441036664415584</v>
+      </c>
+      <c r="E3">
+        <v>-0.006056678831586502</v>
+      </c>
+      <c r="F3">
+        <v>0.001508881736716506</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="n">
+    <row r="4" spans="1:6">
+      <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>[-47.47740411375018, -44.44220053370135, -43.03780891109198, -50.16112259427547, -46.66368019006346]</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>-46.35644326857649</v>
-      </c>
-      <c r="D4" t="n">
-        <v>-46.35644326857649</v>
-      </c>
-      <c r="E4" t="n">
-        <v>-50.16112259427547</v>
-      </c>
-      <c r="F4" t="n">
-        <v>-43.03780891109198</v>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>0.01858975324499745</v>
+      </c>
+      <c r="D4">
+        <v>-0.002700941223399932</v>
+      </c>
+      <c r="E4">
+        <v>-0.007437649408662244</v>
+      </c>
+      <c r="F4">
+        <v>0.002283972810271579</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="n">
+    <row r="5" spans="1:6">
+      <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>[-57.11398467942161, -37.69697917387816, -48.740753735126255, -47.18454383020805, -33.3154093632523]</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>-44.81033415637727</v>
-      </c>
-      <c r="D5" t="n">
-        <v>-44.81033415637727</v>
-      </c>
-      <c r="E5" t="n">
-        <v>-57.11398467942161</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-33.3154093632523</v>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5">
+        <v>0.004377169421967864</v>
+      </c>
+      <c r="D5">
+        <v>-0.0001123257369284422</v>
+      </c>
+      <c r="E5">
+        <v>-0.003149451149432465</v>
+      </c>
+      <c r="F5">
+        <v>0.002647358337207918</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="n">
+    <row r="6" spans="1:6">
+      <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>[-53.95040357869742, -48.10311959038408, -46.3205118564382, -44.03581531851657, -35.91811494600038]</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>-45.66559305800733</v>
-      </c>
-      <c r="D6" t="n">
-        <v>-45.66559305800733</v>
-      </c>
-      <c r="E6" t="n">
-        <v>-53.95040357869742</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-35.91811494600038</v>
+      <c r="B6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6">
+        <v>0.006810792842095736</v>
+      </c>
+      <c r="D6">
+        <v>-0.001338635870387154</v>
+      </c>
+      <c r="E6">
+        <v>-0.00430801040561702</v>
+      </c>
+      <c r="F6">
+        <v>0.0009734866626195625</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/PANDA_POWER/notebooks/results_consolidados.xlsx
+++ b/PANDA_POWER/notebooks/results_consolidados.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>execution</t>
   </si>
@@ -34,19 +34,64 @@
     <t>max_solution</t>
   </si>
   <si>
-    <t>[-0.009947378528738698, 0.004459406837340901, 0.0019962887981140893, 0.0017006735542902576, 0.0033131360891133187]</t>
-  </si>
-  <si>
-    <t>[-0.006056678831586502, 0.0004560268699975623, 0.0015088817367165065, 0.0002216422400582352, -0.0033350553372637213]</t>
-  </si>
-  <si>
-    <t>[-0.007437649408662244, -0.00023859357258367627, -0.004384958754194064, 0.0022839728102715786, -0.0037274771918312556]</t>
-  </si>
-  <si>
-    <t>[0.0016269709884116478, -0.003149451149432465, -0.00011283725843748427, 0.0026473583372079177, -0.0015736696023918272]</t>
-  </si>
-  <si>
-    <t>[0.00041424964700103196, -0.0038276063129415684, 5.470105700222487e-05, 0.0009734866626195625, -0.00430801040561702]</t>
+    <t>[-0.007453853080269499, 0.000856513683495604, -0.0007268560704688245, -0.0149778663764982, 0.00546744363768026]</t>
+  </si>
+  <si>
+    <t>[-0.0011973416008211324, 0.0015160532251436171, 0.0016972486575890233, 0.006859276787567793, 0.00022633178953446187]</t>
+  </si>
+  <si>
+    <t>[0.0035295792207554553, -0.0015716878317282024, -0.00668132543257941, 0.00026082682322300845, -0.00698599699148148]</t>
+  </si>
+  <si>
+    <t>[0.003631168379706246, 0.0013473812511977188, -0.003898479285305713, -0.00021631778919263718, 0.0021732345811607675]</t>
+  </si>
+  <si>
+    <t>[0.0023415221524839087, -0.0010770467800624963, 0.0014267695601054963, 0.005289621577272675, -0.0025168838493823866]</t>
+  </si>
+  <si>
+    <t>[0.0009747948144971721, 0.002300643645156801, -0.0018858482903345, -0.00020841745509685695, 0.002523992616915327]</t>
+  </si>
+  <si>
+    <t>[0.0011708507974777975, -0.0020193832279019022, -0.0001323453045473542, -1.7974830657199736e-05, -0.001003256887870851]</t>
+  </si>
+  <si>
+    <t>[-0.002153992906781984, -7.834528652691033e-05, -0.00532123967696454, -0.0020139972157946807, 0.003404742463761462]</t>
+  </si>
+  <si>
+    <t>[0.0017451830194193073, 0.015557264147331634, 0.0008341061215844242, -8.075574231889413e-05, -0.0014401225389493412]</t>
+  </si>
+  <si>
+    <t>[0.0017408875892261262, 0.0038691941774390455, -0.0032314320503137473, 0.00045648666938107735, 0.0023381752857527527]</t>
+  </si>
+  <si>
+    <t>[0.00029640484256160393, -0.0008979505336615826, 0.0028921541323473823, -0.0017616118341485798, -0.0007163165527956144]</t>
+  </si>
+  <si>
+    <t>[-0.00014564510371561923, 0.0010730793130263828, 0.002504716706489548, -0.00531351763998519, -0.00010567400560716972]</t>
+  </si>
+  <si>
+    <t>[0.0031881685646780733, -0.005307479050660904, -0.00034951206475197956, 0.006042319710828583, 0.014098110420040864]</t>
+  </si>
+  <si>
+    <t>[-0.006245214846115732, -0.00016799332291039804, 0.0001854032423716772, 0.004353506786459859, -0.0009625858273321136]</t>
+  </si>
+  <si>
+    <t>[-0.001046366812466613, -0.0021163118007747938, 0.001420027870891091, 0.0010518127261785588, 0.0006331257692846421]</t>
+  </si>
+  <si>
+    <t>[-0.00022789158010630005, -0.0005424978817716759, 0.0033697490408559627, 0.008524671400925544, 0.001223005951274777]</t>
+  </si>
+  <si>
+    <t>[0.004548034490834185, -0.002309033757470196, -0.0005073716849900919, -0.001752997145778844, 0.005889104705345153]</t>
+  </si>
+  <si>
+    <t>[-0.0036461592441183717, -0.0003056066751722965, -0.0013473858056928575, 0.0013312844778923232, 0.0015145188654475117]</t>
+  </si>
+  <si>
+    <t>[-0.0019177863671498482, -0.001699526136585824, -0.0034254851323280155, 0.0016331812499384302, 0.0072686318304658395]</t>
+  </si>
+  <si>
+    <t>[0.0026380408064058253, -0.003196561967819993, 0.0016030696182250711, -0.0003098813653474308, -0.0028906757832933595]</t>
   </si>
 </sst>
 </file>
@@ -404,7 +449,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -435,16 +480,16 @@
         <v>6</v>
       </c>
       <c r="C2">
-        <v>0.02711170047837008</v>
+        <v>0.06167485579923415</v>
       </c>
       <c r="D2">
-        <v>0.0003044253500239736</v>
+        <v>-0.003366923641212133</v>
       </c>
       <c r="E2">
-        <v>-0.009947378528738698</v>
+        <v>-0.0149778663764982</v>
       </c>
       <c r="F2">
-        <v>0.004459406837340901</v>
+        <v>0.00546744363768026</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -455,16 +500,16 @@
         <v>7</v>
       </c>
       <c r="C3">
-        <v>0.009986053024675812</v>
+        <v>0.01065490592958795</v>
       </c>
       <c r="D3">
-        <v>-0.001441036664415584</v>
+        <v>0.001820313771802753</v>
       </c>
       <c r="E3">
-        <v>-0.006056678831586502</v>
+        <v>-0.001197341600821132</v>
       </c>
       <c r="F3">
-        <v>0.001508881736716506</v>
+        <v>0.006859276787567793</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -475,16 +520,16 @@
         <v>8</v>
       </c>
       <c r="C4">
-        <v>0.01858975324499745</v>
+        <v>0.02151077718611027</v>
       </c>
       <c r="D4">
-        <v>-0.002700941223399932</v>
+        <v>-0.002289720842362126</v>
       </c>
       <c r="E4">
-        <v>-0.007437649408662244</v>
+        <v>-0.00698599699148148</v>
       </c>
       <c r="F4">
-        <v>0.002283972810271579</v>
+        <v>0.003529579220755455</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -495,16 +540,16 @@
         <v>9</v>
       </c>
       <c r="C5">
-        <v>0.004377169421967864</v>
+        <v>0.006937234423933347</v>
       </c>
       <c r="D5">
-        <v>-0.0001123257369284422</v>
+        <v>0.0006073974275132765</v>
       </c>
       <c r="E5">
-        <v>-0.003149451149432465</v>
+        <v>-0.003898479285305713</v>
       </c>
       <c r="F5">
-        <v>0.002647358337207918</v>
+        <v>0.003631168379706246</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -515,16 +560,316 @@
         <v>10</v>
       </c>
       <c r="C6">
-        <v>0.006810792842095736</v>
+        <v>0.008528958721962354</v>
       </c>
       <c r="D6">
-        <v>-0.001338635870387154</v>
+        <v>0.001092796532083439</v>
       </c>
       <c r="E6">
-        <v>-0.00430801040561702</v>
+        <v>-0.002516883849382387</v>
       </c>
       <c r="F6">
-        <v>0.0009734866626195625</v>
+        <v>0.005289621577272675</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7">
+        <v>0.003216593921878896</v>
+      </c>
+      <c r="D7">
+        <v>0.0007410330662275886</v>
+      </c>
+      <c r="E7">
+        <v>-0.0018858482903345</v>
+      </c>
+      <c r="F7">
+        <v>0.002523992616915327</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>0.001284211639930533</v>
+      </c>
+      <c r="D8">
+        <v>-0.0004004218906999019</v>
+      </c>
+      <c r="E8">
+        <v>-0.002019383227901902</v>
+      </c>
+      <c r="F8">
+        <v>0.001170850797477798</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9">
+        <v>0.009643181261997924</v>
+      </c>
+      <c r="D9">
+        <v>-0.001232566524461331</v>
+      </c>
+      <c r="E9">
+        <v>-0.00532123967696454</v>
+      </c>
+      <c r="F9">
+        <v>0.003404742463761462</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10">
+        <v>0.04913350919057713</v>
+      </c>
+      <c r="D10">
+        <v>0.003323135001413425</v>
+      </c>
+      <c r="E10">
+        <v>-0.001440122538949341</v>
+      </c>
+      <c r="F10">
+        <v>0.01555726414733163</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C11">
+        <v>0.006768687986019373</v>
+      </c>
+      <c r="D11">
+        <v>0.001034662334297051</v>
+      </c>
+      <c r="E11">
+        <v>-0.003231432050313747</v>
+      </c>
+      <c r="F11">
+        <v>0.003869194177439046</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12">
+        <v>0.002554268101000901</v>
+      </c>
+      <c r="D12">
+        <v>-3.746398913935813E-05</v>
+      </c>
+      <c r="E12">
+        <v>-0.00176161183414858</v>
+      </c>
+      <c r="F12">
+        <v>0.002892154132347382</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13">
+        <v>0.007080258874488266</v>
+      </c>
+      <c r="D13">
+        <v>-0.0003974081459584097</v>
+      </c>
+      <c r="E13">
+        <v>-0.00531351763998519</v>
+      </c>
+      <c r="F13">
+        <v>0.002504716706489548</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14">
+        <v>0.05427723490289438</v>
+      </c>
+      <c r="D14">
+        <v>0.003534321516026927</v>
+      </c>
+      <c r="E14">
+        <v>-0.005307479050660904</v>
+      </c>
+      <c r="F14">
+        <v>0.01409811042004086</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15">
+        <v>0.01169297963391713</v>
+      </c>
+      <c r="D15">
+        <v>-0.0005673767935053415</v>
+      </c>
+      <c r="E15">
+        <v>-0.006245214846115732</v>
+      </c>
+      <c r="F15">
+        <v>0.004353506786459859</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>20</v>
+      </c>
+      <c r="C16">
+        <v>0.001804814313162595</v>
+      </c>
+      <c r="D16">
+        <v>-1.154244937742301E-05</v>
+      </c>
+      <c r="E16">
+        <v>-0.002116311800774794</v>
+      </c>
+      <c r="F16">
+        <v>0.001420027870891091</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>21</v>
+      </c>
+      <c r="C17">
+        <v>0.01703186139363844</v>
+      </c>
+      <c r="D17">
+        <v>0.002469407386235661</v>
+      </c>
+      <c r="E17">
+        <v>-0.0005424978817716759</v>
+      </c>
+      <c r="F17">
+        <v>0.008524671400925544</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18">
+        <v>0.01270161147539817</v>
+      </c>
+      <c r="D18">
+        <v>0.001173547321588041</v>
+      </c>
+      <c r="E18">
+        <v>-0.002309033757470196</v>
+      </c>
+      <c r="F18">
+        <v>0.005889104705345153</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19">
+        <v>0.00382277550092347</v>
+      </c>
+      <c r="D19">
+        <v>-0.0004906696763287381</v>
+      </c>
+      <c r="E19">
+        <v>-0.003646159244118372</v>
+      </c>
+      <c r="F19">
+        <v>0.001514518865447512</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>24</v>
+      </c>
+      <c r="C20">
+        <v>0.01463952080608877</v>
+      </c>
+      <c r="D20">
+        <v>0.0003718030888681164</v>
+      </c>
+      <c r="E20">
+        <v>-0.003425485132328016</v>
+      </c>
+      <c r="F20">
+        <v>0.00726863183046584</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21">
+        <v>0.00559433595955916</v>
+      </c>
+      <c r="D21">
+        <v>-0.0004312017383659774</v>
+      </c>
+      <c r="E21">
+        <v>-0.003196561967819993</v>
+      </c>
+      <c r="F21">
+        <v>0.002638040806405825</v>
       </c>
     </row>
   </sheetData>
